--- a/artfynd/A 40199-2025 artfynd.xlsx
+++ b/artfynd/A 40199-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>127735479</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127735477</v>
       </c>
       <c r="B4" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40199-2025 artfynd.xlsx
+++ b/artfynd/A 40199-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735480</v>
       </c>
       <c r="B2" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127735479</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127735477</v>
       </c>
       <c r="B4" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40199-2025 artfynd.xlsx
+++ b/artfynd/A 40199-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735480</v>
       </c>
       <c r="B2" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127735479</v>
       </c>
       <c r="B3" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127735477</v>
       </c>
       <c r="B4" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40199-2025 artfynd.xlsx
+++ b/artfynd/A 40199-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>127735479</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127735477</v>
       </c>
       <c r="B4" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40199-2025 artfynd.xlsx
+++ b/artfynd/A 40199-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>127735479</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127735477</v>
       </c>
       <c r="B4" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40199-2025 artfynd.xlsx
+++ b/artfynd/A 40199-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>127735479</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127735477</v>
       </c>
       <c r="B4" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40199-2025 artfynd.xlsx
+++ b/artfynd/A 40199-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735480</v>
       </c>
       <c r="B2" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127735479</v>
       </c>
       <c r="B3" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127735477</v>
       </c>
       <c r="B4" t="n">
-        <v>98387</v>
+        <v>98395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40199-2025 artfynd.xlsx
+++ b/artfynd/A 40199-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735480</v>
       </c>
       <c r="B2" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127735479</v>
       </c>
       <c r="B3" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127735477</v>
       </c>
       <c r="B4" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
